--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5066,37 +5066,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20570227</v>
+        <v>136637449</v>
       </c>
       <c r="B37" t="n">
-        <v>58602</v>
+        <v>58627</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5106,14 +5106,15 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5150,22 +5151,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vinterdräkt. Matningen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5191,33 +5187,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20570227</t>
+          <t>https://artportalen.se/Sighting/136637449</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20559366</v>
+        <v>20570227</v>
       </c>
       <c r="B38" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5227,7 +5223,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5237,7 +5233,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5281,7 +5277,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5291,17 +5287,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5327,38 +5318,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20559366</t>
+          <t>https://artportalen.se/Sighting/20570227</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>23189683</v>
+        <v>20559366</v>
       </c>
       <c r="B39" t="n">
-        <v>58608</v>
+        <v>58636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103051</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5368,7 +5359,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5378,7 +5369,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5417,27 +5408,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
+          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5463,16 +5454,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/23189683</t>
+          <t>https://artportalen.se/Sighting/20559366</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19382751</v>
+        <v>23189683</v>
       </c>
       <c r="B40" t="n">
-        <v>58676</v>
+        <v>58608</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5480,26 +5471,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103055</v>
+        <v>103051</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5538,27 +5544,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5583,6 +5589,127 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23189683</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>19382751</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S41" t="n">
+        <v>62</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>AMNEBYN 1:18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/19382751</t>
         </is>
@@ -5629,6 +5756,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -2325,7 +2325,7 @@
         <v>136451271</v>
       </c>
       <c r="B15" t="n">
-        <v>58477</v>
+        <v>58479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>136637449</v>
       </c>
       <c r="B37" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,27 +801,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>31720130</v>
+        <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>56925</v>
+        <v>57919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100045</v>
+        <v>100011</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,11 +834,14 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>förbiflygande</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -875,27 +878,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-03-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-03-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Från betesfälten mot Vänern.</t>
+          <t>Upptäcktes av Karin Höök då de kretsade vid huset. Subadulta individer. Klart V-ställda vingar då de kretsade runt. Uppvisade ett klart lekbeteende, då de dök ned efter varandra. Flög över 45:an i riktning mot Tösse.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,39 +918,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Karin Höök</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/31720130</t>
+          <t>https://artportalen.se/Sighting/137070410</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19373945</v>
+        <v>31720130</v>
       </c>
       <c r="B4" t="n">
-        <v>57966</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,17 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1006,27 +1004,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2003-05-16</t>
+          <t>2009-03-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2003-05-16</t>
+          <t>2009-03-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>NYBYGGERUD/TRUMNING/LÄTE</t>
+          <t>Från betesfälten mot Vänern.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,33 +1050,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19373945</t>
+          <t>https://artportalen.se/Sighting/31720130</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20455652</v>
+        <v>19373945</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1091,9 +1089,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1132,7 +1135,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1142,7 +1145,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1152,7 +1155,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Endast hörd.</t>
+          <t>NYBYGGERUD/TRUMNING/LÄTE</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,16 +1181,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20455652</t>
+          <t>https://artportalen.se/Sighting/19373945</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20986532</v>
+        <v>20455652</v>
       </c>
       <c r="B6" t="n">
-        <v>57602</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,21 +1198,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100063</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1217,14 +1220,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>sträckande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1263,27 +1261,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-05-28</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-05-28</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Endast hörd. "Kacklande".</t>
+          <t>Endast hörd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,16 +1307,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20986532</t>
+          <t>https://artportalen.se/Sighting/20455652</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19463760</v>
+        <v>20986532</v>
       </c>
       <c r="B7" t="n">
-        <v>57258</v>
+        <v>57602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,31 +1324,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>sträckande O</t>
+          <t>sträckande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,22 +1392,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2004-03-25</t>
+          <t>2005-05-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2004-03-25</t>
+          <t>2005-05-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Endast hörd. "Kacklande".</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,16 +1438,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19463760</t>
+          <t>https://artportalen.se/Sighting/20986532</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43482850</v>
+        <v>19463760</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,16 +1455,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1466,17 +1474,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande O</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1515,27 +1518,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-08-19</t>
+          <t>2004-03-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-08-19</t>
+          <t>2004-03-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>AL, fick se den rakt över huset !</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,39 +1553,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/43482850</t>
+          <t>https://artportalen.se/Sighting/19463760</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19399540</v>
+        <v>43482850</v>
       </c>
       <c r="B9" t="n">
-        <v>57340</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100091</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1598,6 +1596,16 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1636,27 +1644,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2004-04-21</t>
+          <t>2012-08-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2004-04-21</t>
+          <t>2012-08-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Överflygande, lockläte.</t>
+          <t>AL, fick se den rakt över huset !</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,39 +1684,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19399540</t>
+          <t>https://artportalen.se/Sighting/43482850</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40529156</v>
+        <v>19399540</v>
       </c>
       <c r="B10" t="n">
-        <v>57825</v>
+        <v>57340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100096</v>
+        <v>100091</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1719,11 +1727,6 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1762,27 +1765,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-07-27</t>
+          <t>2004-04-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-07-27</t>
+          <t>2004-04-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På hög höjd över huset. Upptäcktes gm. locklätet.</t>
+          <t>Överflygande, lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,16 +1811,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/40529156</t>
+          <t>https://artportalen.se/Sighting/19399540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123403975</v>
+        <v>40529156</v>
       </c>
       <c r="B11" t="n">
-        <v>57903</v>
+        <v>57825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102110</v>
+        <v>100096</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1847,14 +1850,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -1891,17 +1891,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2011-07-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2011-07-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>satt i ett träd precis vid E45:an</t>
+          <t>På hög höjd över huset. Upptäcktes gm. locklätet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,27 +1926,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Bäck</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Bäck</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123403975</t>
+          <t>https://artportalen.se/Sighting/40529156</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134327920</v>
+        <v>123403975</v>
       </c>
       <c r="B12" t="n">
-        <v>57776</v>
+        <v>57903</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,21 +1954,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102118</v>
+        <v>102110</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1966,19 +1976,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2018,27 +2020,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>02:11</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>02:15</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hördes från bergåsen vid Nybyggerud. Bra spel.</t>
+          <t>satt i ett träd precis vid E45:an</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,44 +2045,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Peter Bäck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Peter Bäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134327920</t>
+          <t>https://artportalen.se/Sighting/123403975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19716929</v>
+        <v>134327920</v>
       </c>
       <c r="B13" t="n">
-        <v>57942</v>
+        <v>57776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102119</v>
+        <v>102118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2103,11 +2095,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2144,27 +2147,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Vid holk.</t>
+          <t>Hördes från bergåsen vid Nybyggerud. Bra spel.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,16 +2193,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19716929</t>
+          <t>https://artportalen.se/Sighting/134327920</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18955902</v>
+        <v>19716929</v>
       </c>
       <c r="B14" t="n">
-        <v>57794</v>
+        <v>57942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,21 +2210,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>102119</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2231,7 +2234,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2270,27 +2273,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2004-01-27</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2004-01-27</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Amnebyn 1:18</t>
+          <t>Vid holk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2316,16 +2319,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/18955902</t>
+          <t>https://artportalen.se/Sighting/19716929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136451271</v>
+        <v>18955902</v>
       </c>
       <c r="B15" t="n">
-        <v>58479</v>
+        <v>57794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,16 +2336,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102624</v>
+        <v>102621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2355,22 +2358,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>rastande</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2407,27 +2399,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>"Fågelguiden", Svensson. Upptäcktes p.g.a. det kraftigt vita strecket över ögat. Satt på vår väg utanför huset. Flög upp på träsargen runt kornellen, då sågs väl den bleka blåhaketeckningen på bröstet, näravstånd. Flög strax vidare V-ut.</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,43 +2445,43 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136451271</t>
+          <t>https://artportalen.se/Sighting/18955902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36639635</v>
+        <v>136451271</v>
       </c>
       <c r="B16" t="n">
-        <v>58039</v>
+        <v>58479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102626</v>
+        <v>102624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2499,14 +2491,15 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2543,27 +2536,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På hygget.</t>
+          <t>"Fågelguiden", Svensson. Upptäcktes p.g.a. det kraftigt vita strecket över ögat. Satt på vår väg utanför huset. Flög upp på träsargen runt kornellen, då sågs väl den bleka blåhaketeckningen på bröstet, näravstånd. Flög strax vidare V-ut.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2578,59 +2571,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Höök, Björn Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/36639635</t>
+          <t>https://artportalen.se/Sighting/136451271</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19308969</v>
+        <v>36639635</v>
       </c>
       <c r="B17" t="n">
-        <v>57386</v>
+        <v>58039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102957</v>
+        <v>102626</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartsnäppa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tringa erythropus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2669,7 +2672,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2679,7 +2682,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2689,7 +2692,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>LOCKLÄTE</t>
+          <t>På hygget.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2704,27 +2707,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Erik Höök</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Erik Höök, Björn Höök</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19308969</t>
+          <t>https://artportalen.se/Sighting/36639635</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32164526</v>
+        <v>19308969</v>
       </c>
       <c r="B18" t="n">
-        <v>57546</v>
+        <v>57386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2732,31 +2735,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102963</v>
+        <v>102957</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Svartsnäppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Tringa erythropus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2795,7 +2798,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2805,12 +2808,17 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>LOCKLÄTE</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2836,33 +2844,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/32164526</t>
+          <t>https://artportalen.se/Sighting/19308969</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24309323</v>
+        <v>32164526</v>
       </c>
       <c r="B19" t="n">
-        <v>57802</v>
+        <v>57546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102975</v>
+        <v>102963</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2872,17 +2880,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pulli</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2921,22 +2924,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2006-07-02</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2006-07-17</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2962,33 +2965,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/24309323</t>
+          <t>https://artportalen.se/Sighting/32164526</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19867297</v>
+        <v>24309323</v>
       </c>
       <c r="B20" t="n">
-        <v>57774</v>
+        <v>57802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102976</v>
+        <v>102975</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2998,12 +3001,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3042,22 +3050,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2006-07-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2006-07-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3083,38 +3091,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19867297</t>
+          <t>https://artportalen.se/Sighting/24309323</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20449044</v>
+        <v>19867297</v>
       </c>
       <c r="B21" t="n">
-        <v>57947</v>
+        <v>57774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102977</v>
+        <v>102976</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3124,7 +3132,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3163,7 +3171,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3173,7 +3181,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3204,33 +3212,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20449044</t>
+          <t>https://artportalen.se/Sighting/19867297</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23361936</v>
+        <v>20449044</v>
       </c>
       <c r="B22" t="n">
-        <v>58209</v>
+        <v>57947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102980</v>
+        <v>102977</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3245,7 +3253,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3284,7 +3292,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2006-05-09</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3294,7 +3302,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2006-05-09</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3325,48 +3333,48 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/23361936</t>
+          <t>https://artportalen.se/Sighting/20449044</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19710881</v>
+        <v>23361936</v>
       </c>
       <c r="B23" t="n">
-        <v>58212</v>
+        <v>58209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3405,7 +3413,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3415,7 +3423,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3446,53 +3454,48 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19710881</t>
+          <t>https://artportalen.se/Sighting/23361936</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26759486</v>
+        <v>19710881</v>
       </c>
       <c r="B24" t="n">
-        <v>58541</v>
+        <v>58212</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102987</v>
+        <v>102981</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3531,7 +3534,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2007-05-25</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3541,17 +3544,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2007-05-25</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Holkhäckning i starholk!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3577,16 +3575,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/26759486</t>
+          <t>https://artportalen.se/Sighting/19710881</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19764908</v>
+        <v>26759486</v>
       </c>
       <c r="B25" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3594,31 +3592,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3657,7 +3660,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2004-04-16</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3667,12 +3670,17 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2004-04-16</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Holkhäckning i starholk!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3698,16 +3706,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19764908</t>
+          <t>https://artportalen.se/Sighting/26759486</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21040568</v>
+        <v>19764908</v>
       </c>
       <c r="B26" t="n">
-        <v>58388</v>
+        <v>58497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3715,21 +3723,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3778,7 +3786,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3788,7 +3796,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3819,38 +3827,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/21040568</t>
+          <t>https://artportalen.se/Sighting/19764908</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21091630</v>
+        <v>21040568</v>
       </c>
       <c r="B27" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3860,7 +3868,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3899,7 +3907,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2005-04-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3909,7 +3917,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2005-04-14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3940,38 +3948,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/21091630</t>
+          <t>https://artportalen.se/Sighting/21040568</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>49680576</v>
+        <v>21091630</v>
       </c>
       <c r="B28" t="n">
-        <v>58238</v>
+        <v>58286</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103012</v>
+        <v>103008</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3981,7 +3989,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4020,27 +4028,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Även lockläte. Tomtkryss!</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4060,44 +4063,44 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/49680576</t>
+          <t>https://artportalen.se/Sighting/21091630</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20180506</v>
+        <v>49680576</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4105,14 +4108,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4151,22 +4149,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2005-01-23</t>
+          <t>2014-05-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2005-01-23</t>
+          <t>2014-05-20</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Även lockläte. Tomtkryss!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4186,22 +4189,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20180506</t>
+          <t>https://artportalen.se/Sighting/49680576</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19703687</v>
+        <v>20180506</v>
       </c>
       <c r="B30" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4209,21 +4212,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4231,14 +4234,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4277,7 +4280,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2005-01-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4287,7 +4290,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2005-01-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4318,16 +4321,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19703687</t>
+          <t>https://artportalen.se/Sighting/20180506</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131566195</v>
+        <v>19703687</v>
       </c>
       <c r="B31" t="n">
-        <v>58250</v>
+        <v>58439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4335,21 +4338,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103019</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4357,18 +4360,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4405,17 +4406,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Matningen. Verkar som familjegrupperna har skingrats. Kanske ett häckningspar i närområdet.</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4441,33 +4447,33 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131566195</t>
+          <t>https://artportalen.se/Sighting/19703687</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19266367</v>
+        <v>131566195</v>
       </c>
       <c r="B32" t="n">
-        <v>58112</v>
+        <v>58250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103020</v>
+        <v>103019</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4480,11 +4486,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4521,27 +4534,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Amnebyn 1:18</t>
+          <t>Matningen. Verkar som familjegrupperna har skingrats. Kanske ett häckningspar i närområdet.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4567,16 +4570,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19266367</t>
+          <t>https://artportalen.se/Sighting/131566195</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19369655</v>
+        <v>19266367</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4584,26 +4587,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4642,7 +4650,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4652,7 +4660,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4662,7 +4670,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4688,38 +4696,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19369655</t>
+          <t>https://artportalen.se/Sighting/19266367</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131566149</v>
+        <v>19369655</v>
       </c>
       <c r="B34" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4727,18 +4735,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4775,17 +4771,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Matningen.</t>
+          <t>AMNEBYN 1:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4811,16 +4817,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131566149</t>
+          <t>https://artportalen.se/Sighting/19369655</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132787274</v>
+        <v>131566149</v>
       </c>
       <c r="B35" t="n">
-        <v>58104</v>
+        <v>58131</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4828,21 +4834,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103035</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4898,12 +4904,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4934,33 +4940,33 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132787274</t>
+          <t>https://artportalen.se/Sighting/131566149</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>28993536</v>
+        <v>132787274</v>
       </c>
       <c r="B36" t="n">
-        <v>58353</v>
+        <v>58104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4973,11 +4979,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5014,27 +5027,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bohål i asp.</t>
+          <t>Matningen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5060,33 +5063,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/28993536</t>
+          <t>https://artportalen.se/Sighting/132787274</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136637449</v>
+        <v>28993536</v>
       </c>
       <c r="B37" t="n">
-        <v>58629</v>
+        <v>58353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5099,22 +5102,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5151,17 +5143,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vinterdräkt. Matningen.</t>
+          <t>Bohål i asp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5187,43 +5189,43 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637449</t>
+          <t>https://artportalen.se/Sighting/28993536</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20570227</v>
+        <v>136637449</v>
       </c>
       <c r="B38" t="n">
-        <v>58602</v>
+        <v>58629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5233,14 +5235,15 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5277,22 +5280,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Vinterdräkt. Matningen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5318,33 +5316,33 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20570227</t>
+          <t>https://artportalen.se/Sighting/136637449</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20559366</v>
+        <v>20570227</v>
       </c>
       <c r="B39" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5354,7 +5352,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5364,7 +5362,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5408,7 +5406,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5418,17 +5416,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5454,38 +5447,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20559366</t>
+          <t>https://artportalen.se/Sighting/20570227</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23189683</v>
+        <v>20559366</v>
       </c>
       <c r="B40" t="n">
-        <v>58608</v>
+        <v>58636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103051</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5495,7 +5488,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5505,7 +5498,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5544,27 +5537,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
+          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5590,16 +5583,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/23189683</t>
+          <t>https://artportalen.se/Sighting/20559366</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>19382751</v>
+        <v>23189683</v>
       </c>
       <c r="B41" t="n">
-        <v>58676</v>
+        <v>58608</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5607,26 +5600,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103055</v>
+        <v>103051</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5665,27 +5673,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5710,6 +5718,127 @@
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23189683</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>19382751</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S42" t="n">
+        <v>62</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>AMNEBYN 1:18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/19382751</t>
         </is>
@@ -5757,6 +5886,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57919</v>
+        <v>57932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>136637449</v>
       </c>
       <c r="B38" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57932</v>
+        <v>57934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>136637449</v>
       </c>
       <c r="B38" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -836,11 +836,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57934</v>
+        <v>57944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57944</v>
+        <v>57945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2321,32 +2321,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>18955902</v>
+        <v>137402943</v>
       </c>
       <c r="B15" t="n">
-        <v>57794</v>
+        <v>58063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102621</v>
+        <v>102611</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2354,11 +2354,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2395,27 +2394,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2004-01-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2004-01-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Amnebyn 1:18</t>
+          <t>Förbiflyttande. Vid huset.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2441,16 +2430,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/18955902</t>
+          <t>https://artportalen.se/Sighting/137402943</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136451271</v>
+        <v>18955902</v>
       </c>
       <c r="B16" t="n">
-        <v>58479</v>
+        <v>57794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,16 +2447,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102624</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2480,22 +2469,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>rastande</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2532,27 +2510,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>"Fågelguiden", Svensson. Upptäcktes p.g.a. det kraftigt vita strecket över ögat. Satt på vår väg utanför huset. Flög upp på träsargen runt kornellen, då sågs väl den bleka blåhaketeckningen på bröstet, näravstånd. Flög strax vidare V-ut.</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2578,43 +2556,43 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136451271</t>
+          <t>https://artportalen.se/Sighting/18955902</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>36639635</v>
+        <v>136451271</v>
       </c>
       <c r="B17" t="n">
-        <v>58039</v>
+        <v>58479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102626</v>
+        <v>102624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2624,14 +2602,15 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -2668,27 +2647,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På hygget.</t>
+          <t>"Fågelguiden", Svensson. Upptäcktes p.g.a. det kraftigt vita strecket över ögat. Satt på vår väg utanför huset. Flög upp på träsargen runt kornellen, då sågs väl den bleka blåhaketeckningen på bröstet, näravstånd. Flög strax vidare V-ut.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2703,59 +2682,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Höök, Björn Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/36639635</t>
+          <t>https://artportalen.se/Sighting/136451271</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19308969</v>
+        <v>36639635</v>
       </c>
       <c r="B18" t="n">
-        <v>57386</v>
+        <v>58039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102957</v>
+        <v>102626</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartsnäppa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tringa erythropus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2794,7 +2783,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2804,7 +2793,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2814,7 +2803,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>LOCKLÄTE</t>
+          <t>På hygget.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2829,27 +2818,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Erik Höök</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Erik Höök, Björn Höök</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19308969</t>
+          <t>https://artportalen.se/Sighting/36639635</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32164526</v>
+        <v>19308969</v>
       </c>
       <c r="B19" t="n">
-        <v>57546</v>
+        <v>57386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,31 +2846,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102963</v>
+        <v>102957</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Svartsnäppa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Tringa erythropus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2920,7 +2909,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2930,12 +2919,17 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>LOCKLÄTE</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2961,33 +2955,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/32164526</t>
+          <t>https://artportalen.se/Sighting/19308969</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24309323</v>
+        <v>32164526</v>
       </c>
       <c r="B20" t="n">
-        <v>57802</v>
+        <v>57546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102975</v>
+        <v>102963</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2997,17 +2991,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>pulli</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3046,22 +3035,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2006-07-02</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2006-07-17</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3087,33 +3076,33 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/24309323</t>
+          <t>https://artportalen.se/Sighting/32164526</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19867297</v>
+        <v>24309323</v>
       </c>
       <c r="B21" t="n">
-        <v>57774</v>
+        <v>57802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102976</v>
+        <v>102975</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3123,12 +3112,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3167,22 +3161,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2006-07-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2006-07-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3208,38 +3202,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19867297</t>
+          <t>https://artportalen.se/Sighting/24309323</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20449044</v>
+        <v>19867297</v>
       </c>
       <c r="B22" t="n">
-        <v>57947</v>
+        <v>57774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102977</v>
+        <v>102976</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3249,7 +3243,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3288,7 +3282,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3298,7 +3292,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3329,33 +3323,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20449044</t>
+          <t>https://artportalen.se/Sighting/19867297</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23361936</v>
+        <v>20449044</v>
       </c>
       <c r="B23" t="n">
-        <v>58209</v>
+        <v>57947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102980</v>
+        <v>102977</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3370,7 +3364,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3409,7 +3403,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2006-05-09</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3419,7 +3413,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2006-05-09</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3450,48 +3444,48 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/23361936</t>
+          <t>https://artportalen.se/Sighting/20449044</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19710881</v>
+        <v>23361936</v>
       </c>
       <c r="B24" t="n">
-        <v>58212</v>
+        <v>58209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3530,7 +3524,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3540,7 +3534,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3571,53 +3565,48 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19710881</t>
+          <t>https://artportalen.se/Sighting/23361936</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26759486</v>
+        <v>19710881</v>
       </c>
       <c r="B25" t="n">
-        <v>58541</v>
+        <v>58212</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102987</v>
+        <v>102981</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3656,7 +3645,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2007-05-25</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3666,17 +3655,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2007-05-25</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Holkhäckning i starholk!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3702,16 +3686,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/26759486</t>
+          <t>https://artportalen.se/Sighting/19710881</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19764908</v>
+        <v>26759486</v>
       </c>
       <c r="B26" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3719,31 +3703,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3782,7 +3771,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2004-04-16</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3792,12 +3781,17 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2004-04-16</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Holkhäckning i starholk!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3823,16 +3817,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19764908</t>
+          <t>https://artportalen.se/Sighting/26759486</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21040568</v>
+        <v>19764908</v>
       </c>
       <c r="B27" t="n">
-        <v>58388</v>
+        <v>58497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3840,21 +3834,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3903,7 +3897,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3913,7 +3907,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3944,38 +3938,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/21040568</t>
+          <t>https://artportalen.se/Sighting/19764908</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21091630</v>
+        <v>21040568</v>
       </c>
       <c r="B28" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3985,7 +3979,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4024,7 +4018,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2005-04-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4034,7 +4028,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2005-04-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4065,38 +4059,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/21091630</t>
+          <t>https://artportalen.se/Sighting/21040568</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>49680576</v>
+        <v>21091630</v>
       </c>
       <c r="B29" t="n">
-        <v>58238</v>
+        <v>58286</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103012</v>
+        <v>103008</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4106,7 +4100,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4145,27 +4139,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Även lockläte. Tomtkryss!</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4185,44 +4174,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/49680576</t>
+          <t>https://artportalen.se/Sighting/21091630</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20180506</v>
+        <v>49680576</v>
       </c>
       <c r="B30" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4230,14 +4219,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4276,22 +4260,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2005-01-23</t>
+          <t>2014-05-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2005-01-23</t>
+          <t>2014-05-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Även lockläte. Tomtkryss!</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4311,22 +4300,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20180506</t>
+          <t>https://artportalen.se/Sighting/49680576</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>19703687</v>
+        <v>20180506</v>
       </c>
       <c r="B31" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4334,21 +4323,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4356,14 +4345,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4402,7 +4391,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2005-01-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4412,7 +4401,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2005-01-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4443,16 +4432,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19703687</t>
+          <t>https://artportalen.se/Sighting/20180506</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131566195</v>
+        <v>19703687</v>
       </c>
       <c r="B32" t="n">
-        <v>58250</v>
+        <v>58439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4460,21 +4449,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103019</v>
+        <v>103018</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4482,18 +4471,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4530,17 +4517,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Matningen. Verkar som familjegrupperna har skingrats. Kanske ett häckningspar i närområdet.</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4566,33 +4558,33 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131566195</t>
+          <t>https://artportalen.se/Sighting/19703687</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19266367</v>
+        <v>131566195</v>
       </c>
       <c r="B33" t="n">
-        <v>58112</v>
+        <v>58250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103020</v>
+        <v>103019</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4605,11 +4597,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4646,27 +4645,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Amnebyn 1:18</t>
+          <t>Matningen. Verkar som familjegrupperna har skingrats. Kanske ett häckningspar i närområdet.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4692,16 +4681,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19266367</t>
+          <t>https://artportalen.se/Sighting/131566195</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19369655</v>
+        <v>19266367</v>
       </c>
       <c r="B34" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4709,26 +4698,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4767,7 +4761,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4777,7 +4771,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4787,7 +4781,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4813,38 +4807,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/19369655</t>
+          <t>https://artportalen.se/Sighting/19266367</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131566149</v>
+        <v>19369655</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4852,18 +4846,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4900,17 +4882,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Matningen.</t>
+          <t>AMNEBYN 1:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4936,16 +4928,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131566149</t>
+          <t>https://artportalen.se/Sighting/19369655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132787274</v>
+        <v>131566149</v>
       </c>
       <c r="B36" t="n">
-        <v>58104</v>
+        <v>58131</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4953,21 +4945,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103035</v>
+        <v>103023</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5023,12 +5015,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5059,33 +5051,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132787274</t>
+          <t>https://artportalen.se/Sighting/131566149</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>28993536</v>
+        <v>132787274</v>
       </c>
       <c r="B37" t="n">
-        <v>58353</v>
+        <v>58104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5098,11 +5090,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5139,27 +5138,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bohål i asp.</t>
+          <t>Matningen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5185,33 +5174,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/28993536</t>
+          <t>https://artportalen.se/Sighting/132787274</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136637449</v>
+        <v>28993536</v>
       </c>
       <c r="B38" t="n">
-        <v>58644</v>
+        <v>58353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5224,22 +5213,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5276,17 +5254,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Vinterdräkt. Matningen.</t>
+          <t>Bohål i asp.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5312,43 +5300,43 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637449</t>
+          <t>https://artportalen.se/Sighting/28993536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20570227</v>
+        <v>136637449</v>
       </c>
       <c r="B39" t="n">
-        <v>58602</v>
+        <v>58644</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5358,14 +5346,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -5402,22 +5391,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Vinterdräkt. Matningen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5443,33 +5427,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20570227</t>
+          <t>https://artportalen.se/Sighting/136637449</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20559366</v>
+        <v>20570227</v>
       </c>
       <c r="B40" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5479,7 +5463,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5489,7 +5473,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5533,7 +5517,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5543,17 +5527,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2002-02-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5579,38 +5558,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20559366</t>
+          <t>https://artportalen.se/Sighting/20570227</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>23189683</v>
+        <v>20559366</v>
       </c>
       <c r="B41" t="n">
-        <v>58608</v>
+        <v>58636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103051</v>
+        <v>103044</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5620,7 +5599,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5630,7 +5609,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5669,27 +5648,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
+          <t>Vinterdräkt.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5715,16 +5694,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/23189683</t>
+          <t>https://artportalen.se/Sighting/20559366</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>19382751</v>
+        <v>23189683</v>
       </c>
       <c r="B42" t="n">
-        <v>58676</v>
+        <v>58608</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5732,26 +5711,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103055</v>
+        <v>103051</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5790,27 +5784,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5835,6 +5829,127 @@
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23189683</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>19382751</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S43" t="n">
+        <v>62</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>AMNEBYN 1:18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/19382751</t>
         </is>
@@ -5883,6 +5998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137070410</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>137402943</v>
       </c>
       <c r="B15" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
